--- a/bookings.xlsx
+++ b/bookings.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/efb007622b83a0f1/Huseberg bokning Filer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{77DD5028-3C44-8045-95FB-370A611A7ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28BFCC02-D047-6D42-AA63-CD60929B1429}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{77DD5028-3C44-8045-95FB-370A611A7ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FA5E783-2F7A-1B40-A42E-CFE06CB8B13B}"/>
   <bookViews>
-    <workbookView xWindow="20760" yWindow="5880" windowWidth="27840" windowHeight="16740" xr2:uid="{556093A2-31EF-0449-B8C5-20FE3B5FC57F}"/>
+    <workbookView xWindow="23000" yWindow="1640" windowWidth="27640" windowHeight="21180" xr2:uid="{556093A2-31EF-0449-B8C5-20FE3B5FC57F}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
+    <sheet name="Listor" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t>Hus</t>
   </si>
@@ -70,6 +71,21 @@
   <si>
     <t>Huvudhus</t>
   </si>
+  <si>
+    <t>Topphuset</t>
+  </si>
+  <si>
+    <t>Midsommar</t>
+  </si>
+  <si>
+    <t>Kevin &amp; Alice</t>
+  </si>
+  <si>
+    <t>Lämnar på natten mot den 20</t>
+  </si>
+  <si>
+    <t>PREL</t>
+  </si>
 </sst>
 </file>
 
@@ -78,12 +94,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -107,9 +130,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -125,6 +149,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -449,6 +477,7 @@
   <cols>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -506,16 +535,64 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46191</v>
+      </c>
+      <c r="E4" s="1">
+        <v>46194</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46191</v>
+      </c>
+      <c r="E5" s="1">
+        <v>46192</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46202</v>
+      </c>
+      <c r="E6" s="1">
+        <v>46215</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D7" s="1"/>
@@ -5580,6 +5657,48 @@
     <row r="1272" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D1272" s="1"/>
       <c r="E1272" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E48A5A60-334C-1D48-8BBD-F97063FDCCF6}">
+          <x14:formula1>
+            <xm:f>Listor!$B$4:$B$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A300</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7C3238-0EE4-A54B-99CE-ECB44B2C8D68}">
+  <dimension ref="B2:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bookings.xlsx
+++ b/bookings.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/efb007622b83a0f1/Huseberg bokning Filer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{77DD5028-3C44-8045-95FB-370A611A7ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FA5E783-2F7A-1B40-A42E-CFE06CB8B13B}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{77DD5028-3C44-8045-95FB-370A611A7ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5257117-9447-E04F-B5EC-614ED737641E}"/>
   <bookViews>
-    <workbookView xWindow="23000" yWindow="1640" windowWidth="27640" windowHeight="21180" xr2:uid="{556093A2-31EF-0449-B8C5-20FE3B5FC57F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18040" xr2:uid="{556093A2-31EF-0449-B8C5-20FE3B5FC57F}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
     <sheet name="Listor" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>Hus</t>
   </si>
@@ -85,6 +85,12 @@
   </si>
   <si>
     <t>PREL</t>
+  </si>
+  <si>
+    <t>Jemina &amp; friends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mållgan &amp; flyttlådorna </t>
   </si>
 </sst>
 </file>
@@ -473,7 +479,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B54135E-D597-CB48-BFCD-373BD5C728F6}">
   <dimension ref="A1:F1272"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
@@ -481,22 +487,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -545,7 +551,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="E4" s="1">
         <v>46194</v>
@@ -565,7 +571,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="E5" s="1">
         <v>46192</v>
@@ -595,16 +601,55 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46172</v>
+      </c>
+      <c r="E7" s="1">
+        <v>46176</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46172</v>
+      </c>
+      <c r="E8" s="1">
+        <v>46176</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46172</v>
+      </c>
+      <c r="E9" s="1">
+        <v>46189</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D10" s="1"/>
@@ -5678,7 +5723,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7C3238-0EE4-A54B-99CE-ECB44B2C8D68}">
   <dimension ref="B2:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
